--- a/data/trans_dic/P32E$casa_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,97; 84,02</t>
+          <t>41,1; 84,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 94,04</t>
+          <t>6,26; 93,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,98; 76,29</t>
+          <t>38,82; 77,86</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,11; 72,83</t>
+          <t>23,68; 73,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,54; 80,06</t>
+          <t>24,48; 80,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,69; 70,75</t>
+          <t>30,81; 69,55</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,63; 60,53</t>
+          <t>18,67; 56,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,99; 58,01</t>
+          <t>22,24; 57,73</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,41; 70,51</t>
+          <t>38,42; 69,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 54,8</t>
+          <t>9,8; 53,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,39; 62,56</t>
+          <t>35,89; 61,37</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,51; 86,92</t>
+          <t>45,29; 86,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 76,39</t>
+          <t>18,65; 77,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,52; 79,51</t>
+          <t>42,91; 79,39</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,6</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,3</t>
+          <t>0,0; 57,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 46,4</t>
+          <t>2,76; 44,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,57; 61,64</t>
+          <t>43,47; 61,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,48; 50,58</t>
+          <t>25,26; 52,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,5; 55,89</t>
+          <t>41,15; 56,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7675; 16133</t>
+          <t>7892; 16283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>393; 5857</t>
+          <t>390; 5852</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9913; 19399</t>
+          <t>9872; 19797</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3153; 9935</t>
+          <t>3231; 10069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2852; 9307</t>
+          <t>2846; 9331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8006; 17877</t>
+          <t>7785; 17573</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6041; 17727</t>
+          <t>5468; 16434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6922; 18263</t>
+          <t>7003; 18177</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14078; 27267</t>
+          <t>14855; 26880</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1084; 5817</t>
+          <t>1040; 5726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17443; 30832</t>
+          <t>17687; 30244</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15054; 28750</t>
+          <t>14980; 28683</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1454; 6179</t>
+          <t>1509; 6249</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18326; 32732</t>
+          <t>17665; 32683</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>0; 6637</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6676</t>
+          <t>0; 6945</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>496; 8681</t>
+          <t>517; 8295</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>59811; 86615</t>
+          <t>61086; 86451</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12952; 25710</t>
+          <t>12837; 26644</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77498; 106938</t>
+          <t>78732; 107637</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$casa_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$casa_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,1; 84,8</t>
+          <t>41,54; 85,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 93,97</t>
+          <t>10,07; 84,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,82; 77,86</t>
+          <t>39,96; 79,26</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,68; 73,82</t>
+          <t>25,64; 74,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,48; 80,26</t>
+          <t>25,57; 80,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,81; 69,55</t>
+          <t>33,88; 71,66</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 56,12</t>
+          <t>19,39; 57,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 84,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,24; 57,73</t>
+          <t>20,74; 54,49</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,42; 69,51</t>
+          <t>37,73; 70,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 53,94</t>
+          <t>10,4; 52,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,89; 61,37</t>
+          <t>33,67; 60,2</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,29; 86,72</t>
+          <t>47,73; 86,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,65; 77,26</t>
+          <t>17,0; 77,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,91; 79,39</t>
+          <t>47,34; 80,98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,53</t>
+          <t>0,0; 63,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 44,34</t>
+          <t>2,64; 45,17</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,47; 61,53</t>
+          <t>44,67; 63,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,26; 52,42</t>
+          <t>25,49; 51,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,15; 56,26</t>
+          <t>42,12; 56,78</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>16274</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7892; 16283</t>
+          <t>8488; 17458</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>390; 5852</t>
+          <t>652; 5506</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9872; 19797</t>
+          <t>10754; 21329</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>15022</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3231; 10069</t>
+          <t>3931; 11486</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2846; 9331</t>
+          <t>3421; 10717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7785; 17573</t>
+          <t>9726; 20570</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12939</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5468; 16434</t>
+          <t>6199; 18245</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2198</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7003; 18177</t>
+          <t>7367; 19353</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>26654</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14855; 26880</t>
+          <t>15778; 29305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1040; 5726</t>
+          <t>1543; 7798</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17687; 30244</t>
+          <t>19073; 34104</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>34007</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14980; 28683</t>
+          <t>20079; 36348</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1509; 6249</t>
+          <t>1436; 6582</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17665; 32683</t>
+          <t>23913; 40909</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3602</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6637</t>
+          <t>0; 6084</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6945</t>
+          <t>0; 8538</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>517; 8295</t>
+          <t>519; 8869</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>74005</t>
+          <t>85792</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>108497</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61086; 86451</t>
+          <t>70445; 100006</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12837; 26644</t>
+          <t>15353; 31182</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78732; 107637</t>
+          <t>91799; 123750</t>
         </is>
       </c>
     </row>
